--- a/Team-Data/2007-08/1-8-2007-08.xlsx
+++ b/Team-Data/2007-08/1-8-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,7 +812,7 @@
         <v>19</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
         <v>18</v>
@@ -772,22 +839,22 @@
         <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT2" t="n">
         <v>22</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>21</v>
       </c>
       <c r="AU2" t="n">
         <v>23</v>
@@ -799,13 +866,13 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA2" t="n">
         <v>8</v>
@@ -814,7 +881,7 @@
         <v>21</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>11</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -954,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
@@ -978,7 +1045,7 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX3" t="n">
         <v>25</v>
@@ -993,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -1025,121 +1092,121 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>0.364</v>
+        <v>0.344</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
       </c>
       <c r="I4" t="n">
-        <v>34.7</v>
+        <v>34.4</v>
       </c>
       <c r="J4" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.443</v>
       </c>
       <c r="L4" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.369</v>
+        <v>0.371</v>
       </c>
       <c r="O4" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.697</v>
+        <v>0.696</v>
       </c>
       <c r="R4" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S4" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
         <v>39.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W4" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>94.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.7</v>
+        <v>-5.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
         <v>29</v>
@@ -1154,31 +1221,31 @@
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.394</v>
+        <v>0.406</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="J5" t="n">
-        <v>85.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.418</v>
+        <v>0.417</v>
       </c>
       <c r="L5" t="n">
         <v>5.2</v>
@@ -1237,37 +1304,37 @@
         <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P5" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R5" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
         <v>44</v>
       </c>
       <c r="U5" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y5" t="n">
         <v>5.8</v>
@@ -1276,49 +1343,49 @@
         <v>21.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AC5" t="n">
         <v>-3.4</v>
       </c>
       <c r="AD5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE5" t="n">
         <v>21</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>22</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>23</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
         <v>24</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1339,25 +1406,25 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA5" t="n">
         <v>18</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1407,10 +1474,10 @@
         <v>35.5</v>
       </c>
       <c r="J6" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L6" t="n">
         <v>6.4</v>
@@ -1422,61 +1489,61 @@
         <v>0.349</v>
       </c>
       <c r="O6" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.719</v>
+        <v>0.716</v>
       </c>
       <c r="R6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="T6" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U6" t="n">
         <v>19.1</v>
       </c>
       <c r="V6" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W6" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y6" t="n">
         <v>4.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB6" t="n">
         <v>95.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
@@ -1488,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1497,13 +1564,13 @@
         <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>25</v>
@@ -1524,19 +1591,19 @@
         <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
         <v>19</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>4</v>
@@ -1679,13 +1746,13 @@
         <v>17</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
         <v>4</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1694,13 +1761,13 @@
         <v>21</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
         <v>17</v>
       </c>
       <c r="AU7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,13 +1776,13 @@
         <v>27</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>12</v>
@@ -1873,10 +1940,10 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>2</v>
@@ -1885,7 +1952,7 @@
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>16</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>10.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,7 +2095,7 @@
         <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ9" t="n">
         <v>21</v>
@@ -2043,25 +2110,25 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
         <v>11</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
         <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
         <v>4</v>
@@ -2073,7 +2140,7 @@
         <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2225,13 +2292,13 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO10" t="n">
         <v>15</v>
       </c>
-      <c r="AO10" t="n">
-        <v>14</v>
-      </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>20</v>
@@ -2240,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2252,13 +2319,13 @@
         <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
         <v>22</v>
       </c>
       <c r="AY10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ10" t="n">
         <v>26</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
         <v>17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J11" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L11" t="n">
         <v>6.7</v>
@@ -2329,73 +2396,73 @@
         <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.335</v>
+        <v>0.333</v>
       </c>
       <c r="O11" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
         <v>22.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.737</v>
+        <v>0.734</v>
       </c>
       <c r="R11" t="n">
         <v>12.4</v>
       </c>
       <c r="S11" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T11" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U11" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V11" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="W11" t="n">
         <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
         <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>18</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
         <v>23</v>
@@ -2422,28 +2489,28 @@
         <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA11" t="n">
         <v>24</v>
@@ -2452,7 +2519,7 @@
         <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -2481,82 +2548,82 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
         <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.444</v>
+        <v>0.457</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J12" t="n">
-        <v>86.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.441</v>
       </c>
       <c r="L12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>22.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.361</v>
+        <v>0.365</v>
       </c>
       <c r="O12" t="n">
         <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.743</v>
+        <v>0.747</v>
       </c>
       <c r="R12" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T12" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="W12" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X12" t="n">
         <v>5.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="AA12" t="n">
         <v>21.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.4</v>
+        <v>102.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO12" t="n">
         <v>21</v>
@@ -2598,7 +2665,7 @@
         <v>20</v>
       </c>
       <c r="AQ12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR12" t="n">
         <v>10</v>
@@ -2613,13 +2680,13 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2814,7 @@
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2765,7 +2832,7 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM13" t="n">
         <v>25</v>
@@ -2795,13 +2862,13 @@
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY13" t="n">
         <v>25</v>
@@ -2816,7 +2883,7 @@
         <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -2845,88 +2912,88 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="O14" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="P14" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
       <c r="Q14" t="n">
         <v>0.765</v>
       </c>
       <c r="R14" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S14" t="n">
         <v>34.2</v>
       </c>
       <c r="T14" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.5</v>
+        <v>107.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2938,10 +3005,10 @@
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2953,13 +3020,13 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
@@ -2977,28 +3044,28 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>12</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.294</v>
+        <v>0.303</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J15" t="n">
-        <v>80.2</v>
+        <v>79.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L15" t="n">
         <v>7.8</v>
@@ -3057,55 +3124,55 @@
         <v>21.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O15" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R15" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="S15" t="n">
         <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="U15" t="n">
         <v>20.5</v>
       </c>
       <c r="V15" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="W15" t="n">
         <v>5.6</v>
       </c>
       <c r="X15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB15" t="n">
         <v>100.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.2</v>
+        <v>-3.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3135,10 +3202,10 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
         <v>17</v>
@@ -3147,37 +3214,37 @@
         <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS15" t="n">
         <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU15" t="n">
         <v>21</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
       </c>
       <c r="BA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB15" t="n">
         <v>11</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>10</v>
       </c>
       <c r="BC15" t="n">
         <v>22</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.229</v>
+        <v>0.235</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J16" t="n">
-        <v>76.8</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
         <v>0.461</v>
@@ -3239,10 +3306,10 @@
         <v>13.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O16" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P16" t="n">
         <v>26.5</v>
@@ -3254,43 +3321,43 @@
         <v>9.4</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T16" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="U16" t="n">
         <v>19.7</v>
       </c>
       <c r="V16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X16" t="n">
         <v>5.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA16" t="n">
         <v>22.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="AC16" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF16" t="n">
         <v>29</v>
@@ -3299,10 +3366,10 @@
         <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
@@ -3314,16 +3381,16 @@
         <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN16" t="n">
         <v>20</v>
       </c>
       <c r="AO16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
         <v>30</v>
@@ -3332,7 +3399,7 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3341,25 +3408,25 @@
         <v>26</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
         <v>11</v>
       </c>
-      <c r="BA16" t="n">
-        <v>10</v>
-      </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.412</v>
+        <v>0.394</v>
       </c>
       <c r="H17" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
         <v>5.2</v>
@@ -3421,22 +3488,22 @@
         <v>15.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O17" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R17" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S17" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T17" t="n">
         <v>40.8</v>
@@ -3445,55 +3512,55 @@
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y17" t="n">
         <v>5.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-5.9</v>
+        <v>-6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
         <v>5</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK17" t="n">
         <v>16</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>24</v>
@@ -3514,10 +3581,10 @@
         <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
@@ -3529,7 +3596,7 @@
         <v>19</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
         <v>21</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -3573,70 +3640,70 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.147</v>
+        <v>0.121</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J18" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L18" t="n">
         <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R18" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U18" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="V18" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z18" t="n">
         <v>24</v>
@@ -3645,13 +3712,13 @@
         <v>17.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,7 +3733,7 @@
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
@@ -3696,10 +3763,10 @@
         <v>5</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -3755,19 +3822,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H19" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I19" t="n">
         <v>33.4</v>
@@ -3776,40 +3843,40 @@
         <v>76.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.32</v>
+        <v>0.323</v>
       </c>
       <c r="O19" t="n">
         <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.726</v>
+        <v>0.73</v>
       </c>
       <c r="R19" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T19" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U19" t="n">
         <v>23.4</v>
       </c>
       <c r="V19" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W19" t="n">
         <v>6.7</v>
@@ -3818,31 +3885,31 @@
         <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.59999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.5</v>
+        <v>-4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>5</v>
@@ -3854,13 +3921,13 @@
         <v>29</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>22</v>
       </c>
       <c r="AM19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AN19" t="n">
         <v>29</v>
@@ -3869,43 +3936,43 @@
         <v>8</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>4.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4027,10 +4094,10 @@
         <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ20" t="n">
         <v>8</v>
@@ -4045,7 +4112,7 @@
         <v>7</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>28</v>
@@ -4060,13 +4127,13 @@
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4075,10 +4142,10 @@
         <v>9</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.273</v>
+        <v>0.25</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="J21" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.432</v>
+        <v>0.43</v>
       </c>
       <c r="L21" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="n">
         <v>16.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.333</v>
+        <v>0.33</v>
       </c>
       <c r="O21" t="n">
         <v>18.9</v>
@@ -4158,58 +4225,58 @@
         <v>26.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.708</v>
+        <v>0.707</v>
       </c>
       <c r="R21" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T21" t="n">
         <v>42.3</v>
       </c>
       <c r="U21" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="V21" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W21" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA21" t="n">
         <v>21.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.8</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF21" t="n">
         <v>27</v>
       </c>
-      <c r="AF21" t="n">
-        <v>26</v>
-      </c>
       <c r="AG21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>26</v>
@@ -4218,7 +4285,7 @@
         <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>19</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>13</v>
@@ -4251,25 +4318,25 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>16</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
         <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>0.611</v>
+        <v>0.629</v>
       </c>
       <c r="H22" t="n">
         <v>48.6</v>
       </c>
       <c r="I22" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J22" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.462</v>
@@ -4328,7 +4395,7 @@
         <v>8.9</v>
       </c>
       <c r="M22" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N22" t="n">
         <v>0.355</v>
@@ -4337,25 +4404,25 @@
         <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.718</v>
+        <v>0.714</v>
       </c>
       <c r="R22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="T22" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V22" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W22" t="n">
         <v>6.5</v>
@@ -4364,7 +4431,7 @@
         <v>4.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z22" t="n">
         <v>21.1</v>
@@ -4373,10 +4440,10 @@
         <v>24.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.3</v>
+        <v>103.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4385,16 +4452,16 @@
         <v>7</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH22" t="n">
         <v>3</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>22</v>
@@ -4409,28 +4476,28 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" t="n">
         <v>26</v>
       </c>
       <c r="AR22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV22" t="n">
         <v>16</v>
@@ -4439,13 +4506,13 @@
         <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
         <v>80.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M23" t="n">
         <v>12.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="O23" t="n">
         <v>17.5</v>
@@ -4522,67 +4589,67 @@
         <v>24.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.714</v>
+        <v>0.713</v>
       </c>
       <c r="R23" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="S23" t="n">
         <v>29.3</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U23" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
         <v>15.9</v>
       </c>
       <c r="W23" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="X23" t="n">
         <v>5.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA23" t="n">
         <v>20.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI23" t="n">
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>28</v>
@@ -4591,7 +4658,7 @@
         <v>28</v>
       </c>
       <c r="AN23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO23" t="n">
         <v>22</v>
@@ -4606,16 +4673,16 @@
         <v>4</v>
       </c>
       <c r="AS23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
         <v>7</v>
@@ -4624,7 +4691,7 @@
         <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
         <v>8</v>
@@ -4633,7 +4700,7 @@
         <v>23</v>
       </c>
       <c r="BB23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
         <v>18</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4761,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4776,10 +4843,10 @@
         <v>5</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ24" t="n">
         <v>6</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4806,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
         <v>2</v>
@@ -4818,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -4925,25 +4992,25 @@
         <v>0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI25" t="n">
         <v>20</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -4952,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="AM25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN25" t="n">
         <v>4</v>
@@ -4970,7 +5037,7 @@
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
         <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.394</v>
+        <v>0.375</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5047,37 +5114,37 @@
         <v>35.3</v>
       </c>
       <c r="J26" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M26" t="n">
         <v>16.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="O26" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="P26" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R26" t="n">
         <v>10.2</v>
       </c>
       <c r="S26" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="T26" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="U26" t="n">
         <v>17.9</v>
@@ -5086,13 +5153,13 @@
         <v>16.7</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X26" t="n">
         <v>3.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z26" t="n">
         <v>22.5</v>
@@ -5101,25 +5168,25 @@
         <v>23.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.7</v>
+        <v>97.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
       <c r="AD26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF26" t="n">
         <v>21</v>
       </c>
-      <c r="AE26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>19</v>
-      </c>
       <c r="AG26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>25</v>
@@ -5128,7 +5195,7 @@
         <v>23</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>20</v>
@@ -5137,13 +5204,13 @@
         <v>21</v>
       </c>
       <c r="AN26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>5</v>
@@ -5152,7 +5219,7 @@
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5161,7 +5228,7 @@
         <v>29</v>
       </c>
       <c r="AV26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW26" t="n">
         <v>8</v>
@@ -5179,7 +5246,7 @@
         <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>6.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>4</v>
@@ -5304,7 +5371,7 @@
         <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ27" t="n">
         <v>20</v>
@@ -5334,7 +5401,7 @@
         <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -5393,94 +5460,94 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
         <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.265</v>
+        <v>0.273</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J28" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M28" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.355</v>
+        <v>0.357</v>
       </c>
       <c r="O28" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P28" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
         <v>45.5</v>
       </c>
       <c r="U28" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V28" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="W28" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA28" t="n">
         <v>20.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7</v>
+        <v>-6.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH28" t="n">
         <v>16</v>
@@ -5489,22 +5556,22 @@
         <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL28" t="n">
         <v>25</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>26</v>
       </c>
-      <c r="AM28" t="n">
-        <v>27</v>
-      </c>
       <c r="AN28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
@@ -5513,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5525,10 +5592,10 @@
         <v>17</v>
       </c>
       <c r="AV28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
@@ -5543,7 +5610,7 @@
         <v>21</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC28" t="n">
         <v>28</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>1.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF29" t="n">
         <v>15</v>
       </c>
-      <c r="AF29" t="n">
-        <v>14</v>
-      </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
         <v>23</v>
@@ -5698,7 +5765,7 @@
         <v>20</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>23</v>
@@ -5713,7 +5780,7 @@
         <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
         <v>13</v>
@@ -5728,7 +5795,7 @@
         <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -5757,64 +5824,64 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F30" t="n">
         <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>0.528</v>
+        <v>0.514</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="L30" t="n">
         <v>3.9</v>
       </c>
       <c r="M30" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="O30" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="P30" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="T30" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U30" t="n">
         <v>25.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
@@ -5823,16 +5890,16 @@
         <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.7</v>
+        <v>104.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,10 +5908,10 @@
         <v>12</v>
       </c>
       <c r="AF30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG30" t="n">
         <v>14</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12</v>
       </c>
       <c r="AH30" t="n">
         <v>25</v>
@@ -5865,22 +5932,22 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT30" t="n">
         <v>26</v>
@@ -5892,10 +5959,10 @@
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY30" t="n">
         <v>29</v>
@@ -5904,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
@@ -5939,40 +6006,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
         <v>17</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>0.515</v>
+        <v>0.531</v>
       </c>
       <c r="H31" t="n">
         <v>48.3</v>
       </c>
       <c r="I31" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>82</v>
       </c>
       <c r="K31" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L31" t="n">
         <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O31" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P31" t="n">
         <v>24.4</v>
@@ -5981,61 +6048,61 @@
         <v>0.79</v>
       </c>
       <c r="R31" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>31.1</v>
+        <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="U31" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V31" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W31" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X31" t="n">
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA31" t="n">
         <v>20</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.8</v>
+        <v>100.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG31" t="n">
         <v>12</v>
       </c>
-      <c r="AG31" t="n">
-        <v>13</v>
-      </c>
       <c r="AH31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
         <v>13</v>
@@ -6047,7 +6114,7 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO31" t="n">
         <v>12</v>
@@ -6059,13 +6126,13 @@
         <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
         <v>25</v>
@@ -6074,22 +6141,22 @@
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>4</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC31" t="n">
         <v>11</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-8-2007-08</t>
+          <t>2008-01-08</t>
         </is>
       </c>
     </row>
